--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>{.putawayDate}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1112,8 +1115,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="8" width="30.625" customWidth="1"/>
     <col min="11" max="11" width="15.25" customWidth="1"/>
@@ -1246,6 +1249,11 @@
       </c>
       <c r="T2" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="15:15">
+      <c r="O19" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -37,6 +37,9 @@
     <t>质检类型</t>
   </si>
   <si>
+    <t>单据状态</t>
+  </si>
+  <si>
     <t>质检时效</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>上架数量</t>
   </si>
   <si>
+    <t>质检状态</t>
+  </si>
+  <si>
     <t>上架状态</t>
   </si>
   <si>
@@ -97,6 +103,9 @@
     <t>{.qcTypeName}</t>
   </si>
   <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
     <t>{.qcTimeliness}</t>
   </si>
   <si>
@@ -125,6 +134,9 @@
   </si>
   <si>
     <t>{.putawayQty}</t>
+  </si>
+  <si>
+    <t>{.qcStatusName}</t>
   </si>
   <si>
     <t>{.putawayStatusName}</t>
@@ -1115,19 +1127,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="8" width="30.625" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="12" max="12" width="13.375" customWidth="1"/>
-    <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="13.75" customWidth="1"/>
-    <col min="19" max="19" width="20.375" customWidth="1"/>
-    <col min="21" max="21" width="8.875" customWidth="1"/>
+    <col min="1" max="9" width="30.625" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="13.375" customWidth="1"/>
+    <col min="14" max="14" width="15.5" customWidth="1"/>
+    <col min="15" max="15" width="16.875" customWidth="1"/>
+    <col min="16" max="16" width="13.75" customWidth="1"/>
+    <col min="17" max="17" width="15.375" customWidth="1"/>
+    <col min="18" max="18" width="23.125" customWidth="1"/>
+    <col min="21" max="21" width="20.375" customWidth="1"/>
+    <col min="23" max="23" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:20">
+    <row r="1" customFormat="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1188,72 +1203,84 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="19" spans="15:15">
-      <c r="O19" t="s">
-        <v>40</v>
+    <row r="19" spans="17:17">
+      <c r="Q19" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -40,6 +40,9 @@
     <t>单据状态</t>
   </si>
   <si>
+    <t>作废状态</t>
+  </si>
+  <si>
     <t>质检时效</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
   </si>
   <si>
     <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
   </si>
   <si>
     <t>{.qcTimeliness}</t>
@@ -1127,22 +1133,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="9" width="30.625" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="13.375" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-    <col min="15" max="15" width="16.875" customWidth="1"/>
-    <col min="16" max="16" width="13.75" customWidth="1"/>
-    <col min="17" max="17" width="15.375" customWidth="1"/>
-    <col min="18" max="18" width="23.125" customWidth="1"/>
-    <col min="21" max="21" width="20.375" customWidth="1"/>
-    <col min="23" max="23" width="8.875" customWidth="1"/>
+    <col min="1" max="10" width="30.625" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="15" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="16.875" customWidth="1"/>
+    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="18" max="18" width="15.375" customWidth="1"/>
+    <col min="19" max="19" width="23.125" customWidth="1"/>
+    <col min="22" max="22" width="20.375" customWidth="1"/>
+    <col min="24" max="24" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:22">
+    <row r="1" customFormat="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1209,78 +1215,84 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="19" spans="17:17">
-      <c r="Q19" t="s">
-        <v>44</v>
+    <row r="19" spans="18:18">
+      <c r="R19" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,11 +29,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>质检通知单号</t>
   </si>
   <si>
+    <t>来源单号</t>
+  </si>
+  <si>
+    <t>采购单号</t>
+  </si>
+  <si>
     <t>质检类型</t>
   </si>
   <si>
@@ -55,6 +61,9 @@
     <t>产品名称</t>
   </si>
   <si>
+    <t>供应商</t>
+  </si>
+  <si>
     <t>质检通知数量</t>
   </si>
   <si>
@@ -103,6 +112,12 @@
     <t>{.code}</t>
   </si>
   <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.purchaseOrderCode}</t>
+  </si>
+  <si>
     <t>{.qcTypeName}</t>
   </si>
   <si>
@@ -122,6 +137,9 @@
   </si>
   <si>
     <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.supplierName}</t>
   </si>
   <si>
     <t>{.qcNoticeQty}</t>
@@ -1133,22 +1151,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="10" width="30.625" customWidth="1"/>
-    <col min="13" max="13" width="15.25" customWidth="1"/>
-    <col min="14" max="14" width="13.375" customWidth="1"/>
-    <col min="15" max="15" width="15.5" customWidth="1"/>
-    <col min="16" max="16" width="16.875" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
-    <col min="18" max="18" width="15.375" customWidth="1"/>
-    <col min="19" max="19" width="23.125" customWidth="1"/>
-    <col min="22" max="22" width="20.375" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="13" width="30.625" customWidth="1"/>
+    <col min="16" max="16" width="15.25" customWidth="1"/>
+    <col min="17" max="17" width="13.375" customWidth="1"/>
+    <col min="18" max="18" width="15.5" customWidth="1"/>
+    <col min="19" max="19" width="16.875" customWidth="1"/>
+    <col min="20" max="20" width="13.75" customWidth="1"/>
+    <col min="21" max="21" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="23.125" customWidth="1"/>
+    <col min="25" max="25" width="20.375" customWidth="1"/>
+    <col min="27" max="27" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:23">
+    <row r="1" customFormat="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1218,81 +1236,99 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="19" spans="18:18">
-      <c r="R19" t="s">
-        <v>46</v>
+    <row r="19" spans="21:21">
+      <c r="U19" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,19 +64,19 @@
     <t>供应商</t>
   </si>
   <si>
-    <t>质检通知数量</t>
-  </si>
-  <si>
-    <t>质检数量</t>
+    <t>送检数量</t>
+  </si>
+  <si>
+    <t>抽检数量</t>
   </si>
   <si>
     <t>送检差异</t>
   </si>
   <si>
-    <t>良品数量</t>
-  </si>
-  <si>
-    <t>不良品数量</t>
+    <t>抽检良品数量</t>
+  </si>
+  <si>
+    <t>抽检不良品数量</t>
   </si>
   <si>
     <t>上架数量</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -97,6 +97,9 @@
     <t>质检人</t>
   </si>
   <si>
+    <t>期望质检时间</t>
+  </si>
+  <si>
     <t>创建时间</t>
   </si>
   <si>
@@ -173,6 +176,9 @@
   </si>
   <si>
     <t>{.qcUserName}</t>
+  </si>
+  <si>
+    <t>{.planQcDate}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -1151,7 +1157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="13" width="30.625" customWidth="1"/>
@@ -1162,11 +1168,12 @@
     <col min="20" max="20" width="13.75" customWidth="1"/>
     <col min="21" max="21" width="15.375" customWidth="1"/>
     <col min="22" max="22" width="23.125" customWidth="1"/>
-    <col min="25" max="25" width="20.375" customWidth="1"/>
-    <col min="27" max="27" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="26" max="26" width="20.375" customWidth="1"/>
+    <col min="28" max="28" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:26">
+    <row r="1" customFormat="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1245,90 +1252,96 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="21:21">
       <c r="U19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -97,6 +97,12 @@
     <t>质检人</t>
   </si>
   <si>
+    <t>期望质检日期</t>
+  </si>
+  <si>
+    <t>计划质检日期</t>
+  </si>
+  <si>
     <t>创建时间</t>
   </si>
   <si>
@@ -173,6 +179,12 @@
   </si>
   <si>
     <t>{.qcUserName}</t>
+  </si>
+  <si>
+    <t>{.expectQcDate}</t>
+  </si>
+  <si>
+    <t>{.planQcDate}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -1151,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="13" width="30.625" customWidth="1"/>
@@ -1162,11 +1174,12 @@
     <col min="20" max="20" width="13.75" customWidth="1"/>
     <col min="21" max="21" width="15.375" customWidth="1"/>
     <col min="22" max="22" width="23.125" customWidth="1"/>
-    <col min="25" max="25" width="20.375" customWidth="1"/>
-    <col min="27" max="27" width="8.875" customWidth="1"/>
+    <col min="23" max="24" width="14.375" customWidth="1"/>
+    <col min="27" max="27" width="20.375" customWidth="1"/>
+    <col min="29" max="29" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:26">
+    <row r="1" customFormat="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1245,90 +1258,102 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="21:21">
       <c r="U19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -97,7 +97,7 @@
     <t>质检人</t>
   </si>
   <si>
-    <t>期望质检时间</t>
+    <t>期望质检日期</t>
   </si>
   <si>
     <t>创建时间</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -100,6 +100,9 @@
     <t>期望质检日期</t>
   </si>
   <si>
+    <t>计划质检日期</t>
+  </si>
+  <si>
     <t>创建时间</t>
   </si>
   <si>
@@ -176,6 +179,9 @@
   </si>
   <si>
     <t>{.qcUserName}</t>
+  </si>
+  <si>
+    <t>{.expectQcDate}</t>
   </si>
   <si>
     <t>{.planQcDate}</t>
@@ -1157,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="13" width="30.625" customWidth="1"/>
@@ -1168,12 +1174,13 @@
     <col min="20" max="20" width="13.75" customWidth="1"/>
     <col min="21" max="21" width="15.375" customWidth="1"/>
     <col min="22" max="22" width="23.125" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="20.375" customWidth="1"/>
-    <col min="28" max="28" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="17.125" customWidth="1"/>
+    <col min="24" max="24" width="14.875" customWidth="1"/>
+    <col min="27" max="27" width="20.375" customWidth="1"/>
+    <col min="29" max="29" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:27">
+    <row r="1" customFormat="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1255,93 +1262,99 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="21:21">
       <c r="U19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>{.planQcDate}</t>
+  </si>
+  <si>
+    <t>{.expectQcDate}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -1157,7 +1160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="13" width="30.625" customWidth="1"/>
@@ -1169,11 +1172,12 @@
     <col min="21" max="21" width="15.375" customWidth="1"/>
     <col min="22" max="22" width="23.125" customWidth="1"/>
     <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="20.375" customWidth="1"/>
-    <col min="28" max="28" width="8.875" customWidth="1"/>
+    <col min="24" max="24" width="19.625" customWidth="1"/>
+    <col min="27" max="27" width="20.375" customWidth="1"/>
+    <col min="29" max="29" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:27">
+    <row r="1" customFormat="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1244,19 +1248,22 @@
         <v>22</v>
       </c>
       <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1337,11 +1344,14 @@
       </c>
       <c r="AA2" t="s">
         <v>53</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="21:21">
       <c r="U19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/qcNoticeExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>质检通知单号</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>质检人</t>
+  </si>
+  <si>
+    <t>计划质检日期</t>
   </si>
   <si>
     <t>期望质检日期</t>
@@ -1248,110 +1251,110 @@
         <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AB2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="21:21">
       <c r="U19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
